--- a/Diccionarios/EAM/EAM_2024_Diccionario_Completo.xlsx
+++ b/Diccionarios/EAM/EAM_2024_Diccionario_Completo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Documents\Trabajo-Profesional\Javeriana\Diccionarios\EAM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36E45C01-EB2C-4CB7-A891-3EBFC319B9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B30CC837-8BF4-4B44-AE9F-83DAD557FB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
